--- a/Documentos/CHECKLIST/CHECKLIST_V1.xlsx
+++ b/Documentos/CHECKLIST/CHECKLIST_V1.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/domingues_mateus_pucpr_edu_br/Documents/A-4periodoBES/qualidade de software/Documentos/CHECKLIST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9267E356-D73F-40BD-AEAA-ADC852717269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{9267E356-D73F-40BD-AEAA-ADC852717269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3B53D61-2EED-432D-AE94-1EC301E529E3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CHECKLIST V1.0" sheetId="2" r:id="rId1"/>
     <sheet name="EMAIL_NAO_CONFORMIDADE" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHECKLIST V1.0'!$A$1:$M$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHECKLIST V1.0'!$A$1:$O$88</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
   <si>
     <t>Numero</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Descricao</t>
   </si>
   <si>
-    <t>Foi Realizado?</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
     <t>Prazo Resolucao</t>
   </si>
   <si>
-    <t>Responsavel</t>
-  </si>
-  <si>
     <t>Acao Corretiva</t>
   </si>
   <si>
@@ -159,6 +153,15 @@
     <t>Nas tabelas ("HISTORIA DO USUARIO"): todos os campos PBI foram preenchidos?</t>
   </si>
   <si>
+    <t>Nas tabelas ("HISTORIA DO USUARIO"): no campo COMO/POSSO/PARA foram preenchidos o COMO?</t>
+  </si>
+  <si>
+    <t>Nas tabelas ("HISTORIA DO USUARIO"): no campo COMO/POSSO/PARA foram preenchidos o POSSO?</t>
+  </si>
+  <si>
+    <t>Nas tabelas ("HISTORIA DO USUARIO"): no campo COMO/POSSO/PARA foram preenchidos o PARA?</t>
+  </si>
+  <si>
     <t>Nas tabelas ("HISTORIA DO USUARIO"): todos os campos dos CRITERIOS DE ACEITE foram preenchidos com DADO QUE?</t>
   </si>
   <si>
@@ -168,30 +171,21 @@
     <t>Nas tabelas ("HISTORIA DO USUARIO"): todos os campos dos CRITERIOS DE ACEITE foram preenchidos com ENTAO?</t>
   </si>
   <si>
-    <t>Nas tabelas ("HISTORIA DO USUARIO"): no campo COMO/POSSO/PARA foram preenchidos o COMO?</t>
-  </si>
-  <si>
-    <t>Nas tabelas ("HISTORIA DO USUARIO"): no campo COMO/POSSO/PARA foram preenchidos o POSSO?</t>
-  </si>
-  <si>
-    <t>Nas tabelas ("HISTORIA DO USUARIO"): no campo COMO/POSSO/PARA foram preenchidos o PARA?</t>
-  </si>
-  <si>
     <t>Artefato 6</t>
   </si>
   <si>
+    <t>Foi inserido uma ou mais figuras com o MODELO RELACIONAL ?</t>
+  </si>
+  <si>
     <t>Artefato 7</t>
   </si>
   <si>
+    <t>Foi inserido uma ou mais figuras com o DIAGRAMA DE CLASSES ?</t>
+  </si>
+  <si>
     <t>Artefato 8</t>
   </si>
   <si>
-    <t>Foi inserido uma ou mais figuras com o MODELO RELACIONAL ?</t>
-  </si>
-  <si>
-    <t>Foi inserido uma ou mais figuras com o DIAGRAMA DE CLASSES ?</t>
-  </si>
-  <si>
     <t>Foi inserido uma ou mais figuras com o DIAGRAMA DE ATIVIDADES ?</t>
   </si>
   <si>
@@ -244,6 +238,24 @@
   </si>
   <si>
     <t>...</t>
+  </si>
+  <si>
+    <t>Resultado</t>
+  </si>
+  <si>
+    <t>data e hora da identificacao da NC</t>
+  </si>
+  <si>
+    <t>Responsavel pela resolucao</t>
+  </si>
+  <si>
+    <t>data e hora de escalonamento</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>data e hora da conclusao da NC</t>
   </si>
 </sst>
 </file>
@@ -308,7 +320,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -500,12 +512,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -628,6 +675,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -637,12 +699,9 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -665,18 +724,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -705,14 +767,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1012,27 +1066,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BCBE4-A1E9-46FD-814B-80DFFEF3498D}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" style="8" customWidth="1"/>
     <col min="2" max="2" width="16.5546875" style="9" customWidth="1"/>
     <col min="3" max="3" width="33.5546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.109375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="30" style="8" customWidth="1"/>
-    <col min="6" max="6" width="16.5546875" style="8" customWidth="1"/>
-    <col min="7" max="8" width="16.44140625" style="8" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" style="8" customWidth="1"/>
-    <col min="10" max="10" width="14" style="8" customWidth="1"/>
-    <col min="11" max="12" width="8.88671875" style="8"/>
-    <col min="13" max="13" width="19.21875" style="10" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="8"/>
-    <col min="15" max="15" width="18.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="8"/>
+    <col min="5" max="5" width="18" style="8" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="23.21875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="20.21875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="20.88671875" style="8" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" style="8" customWidth="1"/>
+    <col min="11" max="11" width="24.5546875" style="8" customWidth="1"/>
+    <col min="12" max="12" width="31.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.33203125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="25.21875" style="8" customWidth="1"/>
+    <col min="15" max="15" width="19.33203125" style="10" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="8"/>
+    <col min="17" max="17" width="18.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="7" customFormat="1" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1043,39 +1100,51 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="L1" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="M1" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="N1" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="O1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="17">
         <v>1</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17" t="str">
@@ -1083,25 +1152,29 @@
         <v/>
       </c>
       <c r="F2" s="17"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="20"/>
       <c r="I2" s="17"/>
       <c r="J2" s="17"/>
-      <c r="M2" s="10">
+      <c r="K2" s="17"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="10">
         <f>1 - (COUNTIF(E2:E33,"nao confomidade")/32)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="13">
         <f>A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>13</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13" t="str">
@@ -1113,17 +1186,21 @@
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
       <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+    </row>
+    <row r="4" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13">
         <f t="shared" ref="A4:A69" si="1">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D4" s="13"/>
       <c r="E4" s="13" t="str">
@@ -1135,17 +1212,21 @@
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
       <c r="J4" s="13"/>
-    </row>
-    <row r="5" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+    </row>
+    <row r="5" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="13">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>16</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13" t="str">
@@ -1157,17 +1238,21 @@
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
-    </row>
-    <row r="6" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+    </row>
+    <row r="6" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="13">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13" t="str">
@@ -1179,17 +1264,21 @@
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
-    </row>
-    <row r="7" spans="1:13" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+    </row>
+    <row r="7" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>17</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>19</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13" t="str">
@@ -1201,17 +1290,21 @@
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
-    </row>
-    <row r="8" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+    </row>
+    <row r="8" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13" t="str">
@@ -1219,21 +1312,25 @@
         <v/>
       </c>
       <c r="F8" s="13"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="16"/>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
-    </row>
-    <row r="9" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+    </row>
+    <row r="9" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13" t="str">
@@ -1241,21 +1338,25 @@
         <v/>
       </c>
       <c r="F9" s="13"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="16"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
-    </row>
-    <row r="10" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+    </row>
+    <row r="10" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13" t="str">
@@ -1263,21 +1364,25 @@
         <v/>
       </c>
       <c r="F10" s="13"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="16"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
-    </row>
-    <row r="11" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+    </row>
+    <row r="11" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13" t="str">
@@ -1289,17 +1394,21 @@
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
-    </row>
-    <row r="12" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+    </row>
+    <row r="12" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="B12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>23</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>25</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13" t="str">
@@ -1311,17 +1420,21 @@
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
-    </row>
-    <row r="13" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+    </row>
+    <row r="13" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13" t="str">
@@ -1333,17 +1446,21 @@
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
-    </row>
-    <row r="14" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+    </row>
+    <row r="14" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13" t="str">
@@ -1355,17 +1472,21 @@
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
-    </row>
-    <row r="15" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+    </row>
+    <row r="15" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13" t="str">
@@ -1373,21 +1494,25 @@
         <v/>
       </c>
       <c r="F15" s="13"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="16"/>
       <c r="I15" s="13"/>
       <c r="J15" s="13"/>
-    </row>
-    <row r="16" spans="1:13" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+    </row>
+    <row r="16" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13" t="str">
@@ -1399,17 +1524,21 @@
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
-    </row>
-    <row r="17" spans="1:10" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+    </row>
+    <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13" t="str">
@@ -1421,17 +1550,21 @@
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
-    </row>
-    <row r="18" spans="1:10" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+    </row>
+    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="B18" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>30</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>32</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13" t="str">
@@ -1443,17 +1576,21 @@
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
-    </row>
-    <row r="19" spans="1:10" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+    </row>
+    <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13" t="str">
@@ -1465,17 +1602,21 @@
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
-    </row>
-    <row r="20" spans="1:10" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+    </row>
+    <row r="20" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13" t="str">
@@ -1487,17 +1628,21 @@
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
-    </row>
-    <row r="21" spans="1:10" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+    </row>
+    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13" t="str">
@@ -1509,17 +1654,21 @@
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
-    </row>
-    <row r="22" spans="1:10" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+    </row>
+    <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13" t="str">
@@ -1531,17 +1680,21 @@
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
-    </row>
-    <row r="23" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+    </row>
+    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="13" t="str">
@@ -1553,17 +1706,21 @@
       <c r="H23" s="13"/>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
-    </row>
-    <row r="24" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+    </row>
+    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="B24" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>42</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13" t="str">
@@ -1575,17 +1732,21 @@
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
-    </row>
-    <row r="25" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+    </row>
+    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13" t="str">
@@ -1597,17 +1758,21 @@
       <c r="H25" s="13"/>
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
-    </row>
-    <row r="26" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+    </row>
+    <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13" t="str">
@@ -1619,17 +1784,21 @@
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
-    </row>
-    <row r="27" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+    </row>
+    <row r="27" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
         <f>A24+1</f>
         <v>24</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13" t="str">
@@ -1641,17 +1810,21 @@
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
-    </row>
-    <row r="28" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+    </row>
+    <row r="28" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13" t="str">
@@ -1663,17 +1836,21 @@
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
-    </row>
-    <row r="29" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+    </row>
+    <row r="29" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13" t="str">
@@ -1685,17 +1862,21 @@
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
-    </row>
-    <row r="30" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+    </row>
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13" t="str">
@@ -1707,17 +1888,21 @@
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
-    </row>
-    <row r="31" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+    </row>
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="B31" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>46</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>49</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13" t="str">
@@ -1729,8 +1914,12 @@
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
-    </row>
-    <row r="32" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+    </row>
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -1739,7 +1928,7 @@
         <v>47</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13" t="str">
@@ -1751,17 +1940,21 @@
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
-    </row>
-    <row r="33" spans="1:10" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+    </row>
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13" t="str">
@@ -1769,388 +1962,384 @@
         <v/>
       </c>
       <c r="F33" s="13"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="16"/>
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
-    </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="C45" s="12"/>
-      <c r="G45" s="11"/>
-    </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H45" s="11"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="G52" s="11"/>
-    </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H52" s="11"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="G54" s="11"/>
-    </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H54" s="11"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="G55" s="11"/>
-    </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H55" s="11"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="G57" s="11"/>
-    </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H57" s="11"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <f t="shared" ref="A70:A87" si="2">A69+1</f>
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
     </row>
-    <row r="72" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
     </row>
-    <row r="76" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
     </row>
-    <row r="77" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
     </row>
-    <row r="78" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="G85" s="11"/>
-    </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H85" s="11"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="G86" s="11"/>
-    </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="H86" s="11"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M88" xr:uid="{8C4BCBE4-A1E9-46FD-814B-80DFFEF3498D}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Artefato 5"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:O88" xr:uid="{8C4BCBE4-A1E9-46FD-814B-80DFFEF3498D}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+  <conditionalFormatting sqref="E1:F1048576">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="sim">
+      <formula>NOT(ISERROR(SEARCH("sim",E1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="nao">
+      <formula>NOT(ISERROR(SEARCH("nao",E1)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"nao conformidade"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="nao">
-      <formula>NOT(ISERROR(SEARCH("nao",E1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="sim">
-      <formula>NOT(ISERROR(SEARCH("sim",E1)))</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E87">
-    <cfRule type="expression" dxfId="4" priority="5">
+  <conditionalFormatting sqref="E2:F87">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J87" xr:uid="{49385E11-A38A-47E1-9FB1-4750945AE552}">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K87" xr:uid="{49385E11-A38A-47E1-9FB1-4750945AE552}">
       <formula1>"Sim,Nao"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F34:F92" xr:uid="{BAF74937-7F3A-4633-81D9-E736E4A4E400}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G34:G92" xr:uid="{BAF74937-7F3A-4633-81D9-E736E4A4E400}">
       <formula1>"Advertencia,baixa,media,alta,urgente"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D92" xr:uid="{8A069E69-913B-4A46-82C4-23D23C457A8C}">
       <formula1>"Sim,Não,não se aplica"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F33" xr:uid="{B7A2F41D-64D4-4EB9-8040-EA510C89A5CC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{B7A2F41D-64D4-4EB9-8040-EA510C89A5CC}">
       <formula1>"baixa,media,alta"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N32:N33 N2:N30" xr:uid="{B4D678BB-993B-42E6-B79B-B482868CB43D}">
+      <formula1>"aberto,fechado,fechado por excecao"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -2165,7 +2354,7 @@
   <sheetData>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
@@ -2182,7 +2371,7 @@
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="22"/>
@@ -2199,7 +2388,7 @@
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" s="22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -2216,7 +2405,7 @@
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="22" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -2225,7 +2414,7 @@
       <c r="G6" s="27"/>
       <c r="H6" s="23"/>
       <c r="I6" s="22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J6" s="22"/>
       <c r="K6" s="22"/>
@@ -2235,7 +2424,7 @@
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
@@ -2252,14 +2441,14 @@
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
@@ -2293,13 +2482,13 @@
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H10" s="22"/>
       <c r="I10" s="22"/>
       <c r="J10" s="22"/>
       <c r="K10" s="22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L10" s="22"/>
       <c r="M10" s="22"/>
@@ -2382,20 +2571,20 @@
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H16" s="22"/>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
       <c r="K16" s="22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L16" s="22"/>
       <c r="M16" s="22"/>
@@ -2418,7 +2607,7 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18" s="30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
@@ -2435,7 +2624,7 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" s="34"/>
       <c r="D19" s="34"/>
@@ -2502,17 +2691,13 @@
     <mergeCell ref="K17:N17"/>
     <mergeCell ref="B18:N18"/>
     <mergeCell ref="B19:N22"/>
+    <mergeCell ref="B9:N9"/>
     <mergeCell ref="B11:F15"/>
     <mergeCell ref="G11:J15"/>
     <mergeCell ref="K11:N15"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="K16:N16"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="G8:N8"/>
-    <mergeCell ref="B9:N9"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="K10:N10"/>
@@ -2525,6 +2710,10 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="I6:L6"/>
     <mergeCell ref="M6:N6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="G8:N8"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
